--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9188" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9188" uniqueCount="657">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T05:36:05+00:00</t>
+    <t>2026-07-29T08:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -459,9 +459,6 @@
     <t>iheProblemEntry</t>
   </si>
   <si>
-    <t xml:space="preserve">Conformité Problem Entry (IHE PCC) </t>
-  </si>
-  <si>
     <t>Conformité Problem Entry (IHE PCC)</t>
   </si>
   <si>
@@ -827,7 +824,7 @@
     <t>Observation.languageCode</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/all-languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Observation.value</t>
@@ -4189,7 +4186,7 @@
         <v>144</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4260,7 +4257,7 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>131</v>
@@ -4361,7 +4358,7 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>133</v>
@@ -4464,7 +4461,7 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>135</v>
@@ -4567,7 +4564,7 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>137</v>
@@ -4611,7 +4608,7 @@
         <v>75</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>75</v>
@@ -4670,7 +4667,7 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>141</v>
@@ -4773,13 +4770,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
@@ -4804,10 +4801,10 @@
         <v>96</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4878,7 +4875,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>131</v>
@@ -4979,7 +4976,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>133</v>
@@ -5082,7 +5079,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>135</v>
@@ -5185,7 +5182,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>137</v>
@@ -5229,7 +5226,7 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>75</v>
@@ -5288,7 +5285,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>141</v>
@@ -5391,13 +5388,13 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>75</v>
@@ -5422,10 +5419,10 @@
         <v>96</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5496,7 +5493,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>131</v>
@@ -5597,7 +5594,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>133</v>
@@ -5700,7 +5697,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>135</v>
@@ -5803,7 +5800,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>137</v>
@@ -5847,7 +5844,7 @@
         <v>75</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>75</v>
@@ -5906,7 +5903,7 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>141</v>
@@ -6009,13 +6006,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>75</v>
@@ -6040,10 +6037,10 @@
         <v>96</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6114,7 +6111,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>131</v>
@@ -6215,7 +6212,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>133</v>
@@ -6318,7 +6315,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>135</v>
@@ -6421,7 +6418,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>137</v>
@@ -6465,7 +6462,7 @@
         <v>75</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>75</v>
@@ -6524,7 +6521,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>141</v>
@@ -6627,10 +6624,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6644,7 +6641,7 @@
         <v>76</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>75</v>
@@ -6667,7 +6664,7 @@
         <v>75</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>75</v>
@@ -6686,7 +6683,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>75</v>
@@ -6704,7 +6701,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6724,10 +6721,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6741,7 +6738,7 @@
         <v>76</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>75</v>
@@ -6764,7 +6761,7 @@
         <v>75</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>75</v>
@@ -6783,7 +6780,7 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
@@ -6801,7 +6798,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6821,10 +6818,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6900,7 +6897,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -6920,10 +6917,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6937,7 +6934,7 @@
         <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>75</v>
@@ -6949,10 +6946,10 @@
         <v>96</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7003,7 +7000,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7023,10 +7020,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7049,7 +7046,7 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
@@ -7102,7 +7099,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7122,10 +7119,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7139,7 +7136,7 @@
         <v>76</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>75</v>
@@ -7148,13 +7145,13 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7185,7 +7182,7 @@
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>75</v>
@@ -7203,7 +7200,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7223,10 +7220,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7324,10 +7321,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7343,7 +7340,7 @@
         <v>76</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>75</v>
@@ -7356,7 +7353,7 @@
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7407,7 +7404,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7427,17 +7424,17 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>76</v>
@@ -7446,7 +7443,7 @@
         <v>76</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>75</v>
@@ -7459,7 +7456,7 @@
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7510,7 +7507,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7530,17 +7527,17 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>81</v>
@@ -7562,7 +7559,7 @@
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7613,7 +7610,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -7633,17 +7630,17 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>81</v>
@@ -7665,7 +7662,7 @@
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7716,7 +7713,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -7736,17 +7733,17 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>81</v>
@@ -7755,7 +7752,7 @@
         <v>76</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>75</v>
@@ -7768,7 +7765,7 @@
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7819,7 +7816,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -7839,10 +7836,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7865,11 +7862,11 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7920,7 +7917,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -7940,10 +7937,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7970,7 +7967,7 @@
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8021,7 +8018,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8041,39 +8038,39 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E56" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="F56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K56" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="F56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8124,7 +8121,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8144,17 +8141,17 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>81</v>
@@ -8172,11 +8169,11 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8227,7 +8224,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8247,17 +8244,17 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>81</v>
@@ -8275,11 +8272,11 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8330,7 +8327,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8350,10 +8347,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8376,7 +8373,7 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -8429,7 +8426,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -8449,10 +8446,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8466,7 +8463,7 @@
         <v>76</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>75</v>
@@ -8475,10 +8472,10 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
@@ -8530,7 +8527,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -8550,10 +8547,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8567,7 +8564,7 @@
         <v>76</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>75</v>
@@ -8579,10 +8576,10 @@
         <v>92</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8613,7 +8610,7 @@
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>75</v>
@@ -8631,7 +8628,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -8651,10 +8648,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8752,10 +8749,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8784,7 +8781,7 @@
       </c>
       <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8796,7 +8793,7 @@
         <v>75</v>
       </c>
       <c r="S63" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="T63" t="s" s="2">
         <v>75</v>
@@ -8835,7 +8832,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -8855,17 +8852,17 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>81</v>
@@ -8887,7 +8884,7 @@
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8938,7 +8935,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -8958,17 +8955,17 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>81</v>
@@ -8990,7 +8987,7 @@
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9041,7 +9038,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9061,17 +9058,17 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F66" t="s" s="2">
         <v>81</v>
@@ -9093,7 +9090,7 @@
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9144,7 +9141,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9164,17 +9161,17 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F67" t="s" s="2">
         <v>81</v>
@@ -9196,7 +9193,7 @@
       </c>
       <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9247,7 +9244,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -9267,10 +9264,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9293,11 +9290,11 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9348,7 +9345,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -9368,10 +9365,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9398,7 +9395,7 @@
       </c>
       <c r="L69" s="2"/>
       <c r="M69" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9449,7 +9446,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -9469,39 +9466,39 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E70" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="F70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K70" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="F70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9552,7 +9549,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -9572,39 +9569,39 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E71" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="F71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K71" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="F71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9655,7 +9652,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -9675,17 +9672,17 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F72" t="s" s="2">
         <v>81</v>
@@ -9703,11 +9700,11 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9758,7 +9755,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -9778,10 +9775,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9795,7 +9792,7 @@
         <v>76</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>75</v>
@@ -9804,13 +9801,13 @@
         <v>75</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L73" t="s" s="2">
-        <v>256</v>
-      </c>
       <c r="M73" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9861,7 +9858,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -9881,10 +9878,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9907,7 +9904,7 @@
         <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -9936,11 +9933,11 @@
         <v>75</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>75</v>
@@ -9958,7 +9955,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -9978,10 +9975,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10004,7 +10001,7 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -10057,7 +10054,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -10077,10 +10074,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10136,7 +10133,7 @@
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>75</v>
@@ -10154,7 +10151,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -10174,10 +10171,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10191,7 +10188,7 @@
         <v>76</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>75</v>
@@ -10200,10 +10197,10 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -10235,7 +10232,7 @@
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>75</v>
@@ -10253,7 +10250,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -10273,10 +10270,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10374,10 +10371,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10406,7 +10403,7 @@
       </c>
       <c r="L79" s="2"/>
       <c r="M79" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10457,7 +10454,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -10477,17 +10474,17 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F80" t="s" s="2">
         <v>81</v>
@@ -10509,7 +10506,7 @@
       </c>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -10560,7 +10557,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -10580,17 +10577,17 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F81" t="s" s="2">
         <v>81</v>
@@ -10612,7 +10609,7 @@
       </c>
       <c r="L81" s="2"/>
       <c r="M81" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10663,7 +10660,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -10683,17 +10680,17 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F82" t="s" s="2">
         <v>81</v>
@@ -10715,7 +10712,7 @@
       </c>
       <c r="L82" s="2"/>
       <c r="M82" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10766,7 +10763,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -10786,17 +10783,17 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>81</v>
@@ -10818,7 +10815,7 @@
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -10869,7 +10866,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -10889,10 +10886,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10915,11 +10912,11 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10970,7 +10967,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -10990,10 +10987,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11020,7 +11017,7 @@
       </c>
       <c r="L85" s="2"/>
       <c r="M85" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11071,7 +11068,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -11091,39 +11088,39 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E86" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="F86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K86" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="F86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11174,7 +11171,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -11194,10 +11191,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11295,17 +11292,17 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>81</v>
@@ -11327,7 +11324,7 @@
       </c>
       <c r="L88" s="2"/>
       <c r="M88" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11358,25 +11355,25 @@
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -11396,39 +11393,39 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E89" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="F89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K89" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="F89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11479,7 +11476,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -11499,17 +11496,17 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F90" t="s" s="2">
         <v>81</v>
@@ -11531,7 +11528,7 @@
       </c>
       <c r="L90" s="2"/>
       <c r="M90" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -11562,25 +11559,25 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF90" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -11600,17 +11597,17 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F91" t="s" s="2">
         <v>81</v>
@@ -11632,7 +11629,7 @@
       </c>
       <c r="L91" s="2"/>
       <c r="M91" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -11683,7 +11680,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -11703,17 +11700,17 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F92" t="s" s="2">
         <v>81</v>
@@ -11735,7 +11732,7 @@
       </c>
       <c r="L92" s="2"/>
       <c r="M92" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -11762,29 +11759,29 @@
         <v>75</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -11804,10 +11801,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11863,25 +11860,25 @@
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -11901,10 +11898,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11930,13 +11927,13 @@
         <v>103</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -11986,7 +11983,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -12006,39 +12003,39 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E95" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="F95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K95" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="F95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12089,7 +12086,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -12109,17 +12106,17 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F96" t="s" s="2">
         <v>81</v>
@@ -12137,11 +12134,11 @@
         <v>75</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -12192,19 +12189,19 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>75</v>
@@ -12212,17 +12209,17 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F97" t="s" s="2">
         <v>81</v>
@@ -12240,11 +12237,11 @@
         <v>75</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -12295,7 +12292,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -12315,17 +12312,17 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F98" t="s" s="2">
         <v>81</v>
@@ -12343,11 +12340,11 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -12398,7 +12395,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -12418,10 +12415,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12444,7 +12441,7 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -12477,7 +12474,7 @@
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>75</v>
@@ -12495,7 +12492,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -12515,10 +12512,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12541,7 +12538,7 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -12570,11 +12567,11 @@
         <v>75</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>75</v>
@@ -12592,7 +12589,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -12612,10 +12609,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12638,11 +12635,11 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -12693,7 +12690,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -12713,10 +12710,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12739,7 +12736,7 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -12792,7 +12789,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -12812,10 +12809,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12838,7 +12835,7 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -12891,7 +12888,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -12911,10 +12908,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12937,7 +12934,7 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -12990,7 +12987,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -13010,10 +13007,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13036,7 +13033,7 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -13089,7 +13086,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -13109,10 +13106,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13135,7 +13132,7 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -13188,7 +13185,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -13208,10 +13205,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13225,7 +13222,7 @@
         <v>76</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>75</v>
@@ -13234,13 +13231,13 @@
         <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L107" t="s" s="2">
-        <v>340</v>
-      </c>
       <c r="M107" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -13291,7 +13288,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -13311,10 +13308,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13412,10 +13409,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13513,10 +13510,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13614,10 +13611,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13715,10 +13712,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13818,10 +13815,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13921,10 +13918,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14024,10 +14021,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14127,10 +14124,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14228,10 +14225,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14268,7 +14265,7 @@
         <v>75</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>75</v>
@@ -14287,25 +14284,25 @@
       </c>
       <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF117" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
@@ -14325,10 +14322,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14362,7 +14359,7 @@
       </c>
       <c r="Q118" s="2"/>
       <c r="R118" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="S118" t="s" s="2">
         <v>75</v>
@@ -14384,25 +14381,25 @@
       </c>
       <c r="Y118" s="2"/>
       <c r="Z118" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF118" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -14422,10 +14419,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14448,7 +14445,7 @@
         <v>75</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
@@ -14501,7 +14498,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -14521,10 +14518,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14547,7 +14544,7 @@
         <v>75</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -14600,7 +14597,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -14620,10 +14617,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14646,7 +14643,7 @@
         <v>75</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
@@ -14699,7 +14696,7 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -14719,10 +14716,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14736,7 +14733,7 @@
         <v>76</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>75</v>
@@ -14745,7 +14742,7 @@
         <v>75</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
@@ -14798,7 +14795,7 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -14818,10 +14815,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14919,10 +14916,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15020,10 +15017,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15121,10 +15118,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15222,10 +15219,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15325,10 +15322,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15428,10 +15425,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15531,10 +15528,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15634,10 +15631,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15735,10 +15732,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15768,14 +15765,14 @@
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>75</v>
@@ -15794,25 +15791,25 @@
       </c>
       <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF132" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -15832,10 +15829,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15911,7 +15908,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -15931,10 +15928,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15957,7 +15954,7 @@
         <v>75</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -16010,7 +16007,7 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -16030,10 +16027,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16056,7 +16053,7 @@
         <v>75</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -16085,29 +16082,29 @@
         <v>75</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF135" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -16127,10 +16124,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16153,7 +16150,7 @@
         <v>75</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -16206,7 +16203,7 @@
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -16226,10 +16223,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16252,7 +16249,7 @@
         <v>75</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -16305,7 +16302,7 @@
         <v>75</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -16325,10 +16322,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16351,7 +16348,7 @@
         <v>75</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -16404,7 +16401,7 @@
         <v>75</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -16424,10 +16421,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16450,7 +16447,7 @@
         <v>75</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -16503,7 +16500,7 @@
         <v>75</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -16523,10 +16520,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16549,7 +16546,7 @@
         <v>75</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -16602,7 +16599,7 @@
         <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -16622,10 +16619,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16723,10 +16720,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16824,10 +16821,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16925,10 +16922,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17026,10 +17023,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17129,10 +17126,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17232,10 +17229,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17335,10 +17332,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17438,10 +17435,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17539,10 +17536,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17572,14 +17569,14 @@
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q150" s="2"/>
       <c r="R150" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S150" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="T150" t="s" s="2">
         <v>75</v>
@@ -17598,25 +17595,25 @@
       </c>
       <c r="Y150" s="2"/>
       <c r="Z150" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF150" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AA150" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB150" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC150" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD150" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE150" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF150" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -17636,10 +17633,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17673,7 +17670,7 @@
       </c>
       <c r="Q151" s="2"/>
       <c r="R151" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="S151" t="s" s="2">
         <v>75</v>
@@ -17695,25 +17692,25 @@
       </c>
       <c r="Y151" s="2"/>
       <c r="Z151" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF151" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -17733,10 +17730,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17759,13 +17756,13 @@
         <v>75</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -17792,29 +17789,29 @@
         <v>75</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Y152" s="2"/>
       <c r="Z152" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF152" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -17834,10 +17831,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17935,10 +17932,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17967,7 +17964,7 @@
       </c>
       <c r="L154" s="2"/>
       <c r="M154" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -18018,7 +18015,7 @@
         <v>75</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -18038,17 +18035,17 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E155" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F155" t="s" s="2">
         <v>81</v>
@@ -18070,7 +18067,7 @@
       </c>
       <c r="L155" s="2"/>
       <c r="M155" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -18121,7 +18118,7 @@
         <v>75</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -18141,17 +18138,17 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E156" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F156" t="s" s="2">
         <v>81</v>
@@ -18173,7 +18170,7 @@
       </c>
       <c r="L156" s="2"/>
       <c r="M156" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -18224,7 +18221,7 @@
         <v>75</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -18244,17 +18241,17 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E157" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F157" t="s" s="2">
         <v>81</v>
@@ -18276,7 +18273,7 @@
       </c>
       <c r="L157" s="2"/>
       <c r="M157" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -18327,7 +18324,7 @@
         <v>75</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -18347,17 +18344,17 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E158" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F158" t="s" s="2">
         <v>81</v>
@@ -18379,7 +18376,7 @@
       </c>
       <c r="L158" s="2"/>
       <c r="M158" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -18430,7 +18427,7 @@
         <v>75</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -18450,10 +18447,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18476,11 +18473,11 @@
         <v>75</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L159" s="2"/>
       <c r="M159" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -18531,7 +18528,7 @@
         <v>75</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
@@ -18551,10 +18548,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18581,7 +18578,7 @@
       </c>
       <c r="L160" s="2"/>
       <c r="M160" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -18632,7 +18629,7 @@
         <v>75</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
@@ -18652,39 +18649,39 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E161" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="F161" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G161" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H161" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I161" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J161" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K161" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="F161" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G161" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H161" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I161" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J161" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K161" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="L161" s="2"/>
       <c r="M161" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -18735,7 +18732,7 @@
         <v>75</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>81</v>
@@ -18755,10 +18752,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18856,17 +18853,17 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E163" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F163" t="s" s="2">
         <v>81</v>
@@ -18888,7 +18885,7 @@
       </c>
       <c r="L163" s="2"/>
       <c r="M163" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -18919,25 +18916,25 @@
       </c>
       <c r="Y163" s="2"/>
       <c r="Z163" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA163" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB163" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC163" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD163" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE163" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF163" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AA163" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB163" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC163" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD163" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE163" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF163" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -18957,39 +18954,39 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E164" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="F164" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G164" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H164" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I164" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J164" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K164" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="F164" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G164" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H164" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I164" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J164" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K164" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="L164" s="2"/>
       <c r="M164" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -19040,7 +19037,7 @@
         <v>75</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
@@ -19060,17 +19057,17 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E165" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F165" t="s" s="2">
         <v>81</v>
@@ -19092,7 +19089,7 @@
       </c>
       <c r="L165" s="2"/>
       <c r="M165" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -19123,25 +19120,25 @@
       </c>
       <c r="Y165" s="2"/>
       <c r="Z165" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AA165" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB165" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC165" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD165" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE165" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF165" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AA165" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB165" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC165" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD165" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE165" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF165" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -19161,17 +19158,17 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E166" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F166" t="s" s="2">
         <v>81</v>
@@ -19193,7 +19190,7 @@
       </c>
       <c r="L166" s="2"/>
       <c r="M166" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -19244,7 +19241,7 @@
         <v>75</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -19264,17 +19261,17 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E167" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F167" t="s" s="2">
         <v>81</v>
@@ -19296,7 +19293,7 @@
       </c>
       <c r="L167" s="2"/>
       <c r="M167" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -19323,29 +19320,29 @@
         <v>75</v>
       </c>
       <c r="X167" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Y167" s="2"/>
       <c r="Z167" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AA167" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB167" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC167" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD167" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE167" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF167" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AA167" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB167" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC167" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD167" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE167" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF167" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -19365,10 +19362,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19424,25 +19421,25 @@
       </c>
       <c r="Y168" s="2"/>
       <c r="Z168" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AA168" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB168" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD168" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE168" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF168" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AA168" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB168" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC168" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD168" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE168" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF168" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -19462,10 +19459,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19491,13 +19488,13 @@
         <v>103</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M169" t="s" s="2">
+      <c r="N169" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -19547,7 +19544,7 @@
         <v>75</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
@@ -19567,39 +19564,39 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E170" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="F170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H170" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I170" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J170" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K170" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="F170" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G170" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H170" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I170" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J170" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K170" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="L170" s="2"/>
       <c r="M170" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -19650,7 +19647,7 @@
         <v>75</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
@@ -19670,17 +19667,17 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E171" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F171" t="s" s="2">
         <v>81</v>
@@ -19698,11 +19695,11 @@
         <v>75</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L171" s="2"/>
       <c r="M171" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -19753,19 +19750,19 @@
         <v>75</v>
       </c>
       <c r="AF171" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AG171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI171" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ171" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AG171" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH171" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI171" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ171" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>75</v>
@@ -19773,39 +19770,39 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E172" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="F172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H172" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I172" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J172" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K172" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="F172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G172" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H172" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I172" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J172" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K172" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="L172" s="2"/>
       <c r="M172" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -19856,7 +19853,7 @@
         <v>75</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>
@@ -19876,17 +19873,17 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E173" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F173" t="s" s="2">
         <v>81</v>
@@ -19904,11 +19901,11 @@
         <v>75</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L173" s="2"/>
       <c r="M173" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -19959,7 +19956,7 @@
         <v>75</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
@@ -19979,10 +19976,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -20005,7 +20002,7 @@
         <v>75</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
@@ -20058,7 +20055,7 @@
         <v>75</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -20078,10 +20075,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20104,10 +20101,10 @@
         <v>75</v>
       </c>
       <c r="K175" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L175" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="L175" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
@@ -20159,7 +20156,7 @@
         <v>75</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -20179,10 +20176,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20205,11 +20202,11 @@
         <v>75</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L176" s="2"/>
       <c r="M176" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -20260,7 +20257,7 @@
         <v>75</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
@@ -20280,10 +20277,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20306,7 +20303,7 @@
         <v>75</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L177" s="2"/>
       <c r="M177" s="2"/>
@@ -20359,7 +20356,7 @@
         <v>75</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
@@ -20379,10 +20376,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20405,7 +20402,7 @@
         <v>75</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L178" s="2"/>
       <c r="M178" s="2"/>
@@ -20458,7 +20455,7 @@
         <v>75</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
@@ -20478,10 +20475,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20495,7 +20492,7 @@
         <v>82</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>75</v>
@@ -20504,7 +20501,7 @@
         <v>75</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L179" s="2"/>
       <c r="M179" s="2"/>
@@ -20545,7 +20542,7 @@
         <v>75</v>
       </c>
       <c r="AB179" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AC179" s="2"/>
       <c r="AD179" t="s" s="2">
@@ -20555,7 +20552,7 @@
         <v>125</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
@@ -20575,13 +20572,13 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C180" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="C180" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="D180" t="s" s="2">
         <v>75</v>
@@ -20603,10 +20600,10 @@
         <v>75</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="M180" s="2"/>
       <c r="N180" s="2"/>
@@ -20658,7 +20655,7 @@
         <v>75</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
@@ -20678,10 +20675,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B181" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="B181" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20779,10 +20776,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B182" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="B182" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20880,10 +20877,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B183" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="B183" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -20981,10 +20978,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B184" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="B184" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -21082,10 +21079,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B185" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="B185" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -21185,10 +21182,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B186" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="B186" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -21288,10 +21285,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B187" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="B187" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -21391,10 +21388,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B188" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="B188" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -21494,10 +21491,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B189" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21595,10 +21592,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B190" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -21635,7 +21632,7 @@
         <v>75</v>
       </c>
       <c r="S190" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="T190" t="s" s="2">
         <v>75</v>
@@ -21654,25 +21651,25 @@
       </c>
       <c r="Y190" s="2"/>
       <c r="Z190" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AA190" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB190" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC190" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD190" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE190" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF190" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AA190" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB190" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC190" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD190" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE190" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF190" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>76</v>
@@ -21692,10 +21689,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B191" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21722,7 +21719,7 @@
       </c>
       <c r="L191" s="2"/>
       <c r="M191" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
@@ -21773,7 +21770,7 @@
         <v>75</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>81</v>
@@ -21793,10 +21790,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B192" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21823,12 +21820,12 @@
       </c>
       <c r="L192" s="2"/>
       <c r="M192" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Q192" s="2"/>
       <c r="R192" t="s" s="2">
@@ -21874,7 +21871,7 @@
         <v>75</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>81</v>
@@ -21894,10 +21891,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B193" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="B193" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -21973,7 +21970,7 @@
         <v>75</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>81</v>
@@ -21993,10 +21990,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B194" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="B194" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -22019,7 +22016,7 @@
         <v>75</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L194" s="2"/>
       <c r="M194" s="2"/>
@@ -22072,7 +22069,7 @@
         <v>75</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>81</v>
@@ -22092,10 +22089,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="B195" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -22118,7 +22115,7 @@
         <v>75</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L195" s="2"/>
       <c r="M195" s="2"/>
@@ -22171,7 +22168,7 @@
         <v>75</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>81</v>
@@ -22191,10 +22188,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B196" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -22217,7 +22214,7 @@
         <v>75</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L196" s="2"/>
       <c r="M196" s="2"/>
@@ -22270,7 +22267,7 @@
         <v>75</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>81</v>
@@ -22290,10 +22287,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B197" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="B197" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -22316,7 +22313,7 @@
         <v>75</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="L197" s="2"/>
       <c r="M197" s="2"/>
@@ -22369,7 +22366,7 @@
         <v>75</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>81</v>
@@ -22389,10 +22386,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B198" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="B198" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -22415,7 +22412,7 @@
         <v>75</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L198" s="2"/>
       <c r="M198" s="2"/>
@@ -22468,7 +22465,7 @@
         <v>75</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>81</v>
@@ -22488,10 +22485,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B199" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="B199" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22514,7 +22511,7 @@
         <v>75</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L199" s="2"/>
       <c r="M199" s="2"/>
@@ -22567,7 +22564,7 @@
         <v>75</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>81</v>
@@ -22587,10 +22584,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B200" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="B200" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -22613,7 +22610,7 @@
         <v>75</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L200" s="2"/>
       <c r="M200" s="2"/>
@@ -22666,7 +22663,7 @@
         <v>75</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>81</v>
@@ -22686,10 +22683,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B201" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="B201" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -22712,7 +22709,7 @@
         <v>75</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L201" s="2"/>
       <c r="M201" s="2"/>
@@ -22765,7 +22762,7 @@
         <v>75</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>81</v>
@@ -22785,10 +22782,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B202" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="B202" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -22811,7 +22808,7 @@
         <v>75</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L202" s="2"/>
       <c r="M202" s="2"/>
@@ -22864,7 +22861,7 @@
         <v>75</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>81</v>
@@ -22884,10 +22881,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B203" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="B203" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -22910,7 +22907,7 @@
         <v>75</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L203" s="2"/>
       <c r="M203" s="2"/>
@@ -22963,7 +22960,7 @@
         <v>75</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>81</v>
@@ -22983,10 +22980,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B204" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="B204" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -23009,7 +23006,7 @@
         <v>75</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="L204" s="2"/>
       <c r="M204" s="2"/>
@@ -23062,7 +23059,7 @@
         <v>75</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>81</v>
@@ -23082,13 +23079,13 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B205" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C205" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="B205" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="C205" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="D205" t="s" s="2">
         <v>75</v>
@@ -23110,10 +23107,10 @@
         <v>75</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M205" s="2"/>
       <c r="N205" s="2"/>
@@ -23165,7 +23162,7 @@
         <v>75</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>81</v>
@@ -23185,10 +23182,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -23286,10 +23283,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -23387,10 +23384,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -23488,10 +23485,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -23589,10 +23586,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -23692,10 +23689,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -23795,10 +23792,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -23898,10 +23895,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -24001,10 +23998,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -24102,10 +24099,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -24142,7 +24139,7 @@
         <v>75</v>
       </c>
       <c r="S215" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="T215" t="s" s="2">
         <v>75</v>
@@ -24161,25 +24158,25 @@
       </c>
       <c r="Y215" s="2"/>
       <c r="Z215" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AA215" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB215" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC215" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD215" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE215" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF215" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AA215" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB215" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC215" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD215" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE215" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF215" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>76</v>
@@ -24199,10 +24196,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24229,7 +24226,7 @@
       </c>
       <c r="L216" s="2"/>
       <c r="M216" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
@@ -24280,7 +24277,7 @@
         <v>75</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>81</v>
@@ -24300,10 +24297,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24330,12 +24327,12 @@
       </c>
       <c r="L217" s="2"/>
       <c r="M217" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Q217" s="2"/>
       <c r="R217" t="s" s="2">
@@ -24381,7 +24378,7 @@
         <v>75</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>81</v>
@@ -24401,10 +24398,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -24480,7 +24477,7 @@
         <v>75</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>81</v>
@@ -24500,10 +24497,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -24526,7 +24523,7 @@
         <v>75</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L219" s="2"/>
       <c r="M219" s="2"/>
@@ -24579,7 +24576,7 @@
         <v>75</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>81</v>
@@ -24599,10 +24596,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -24625,7 +24622,7 @@
         <v>75</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L220" s="2"/>
       <c r="M220" s="2"/>
@@ -24678,7 +24675,7 @@
         <v>75</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>81</v>
@@ -24698,10 +24695,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -24724,7 +24721,7 @@
         <v>75</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L221" s="2"/>
       <c r="M221" s="2"/>
@@ -24777,7 +24774,7 @@
         <v>75</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>81</v>
@@ -24797,10 +24794,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -24823,7 +24820,7 @@
         <v>75</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="L222" s="2"/>
       <c r="M222" s="2"/>
@@ -24876,7 +24873,7 @@
         <v>75</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>81</v>
@@ -24896,10 +24893,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -24922,7 +24919,7 @@
         <v>75</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L223" s="2"/>
       <c r="M223" s="2"/>
@@ -24975,7 +24972,7 @@
         <v>75</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
@@ -24995,10 +24992,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -25021,7 +25018,7 @@
         <v>75</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L224" s="2"/>
       <c r="M224" s="2"/>
@@ -25074,7 +25071,7 @@
         <v>75</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>81</v>
@@ -25094,10 +25091,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -25120,7 +25117,7 @@
         <v>75</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L225" s="2"/>
       <c r="M225" s="2"/>
@@ -25173,7 +25170,7 @@
         <v>75</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>81</v>
@@ -25193,10 +25190,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -25219,7 +25216,7 @@
         <v>75</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L226" s="2"/>
       <c r="M226" s="2"/>
@@ -25272,7 +25269,7 @@
         <v>75</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>81</v>
@@ -25292,10 +25289,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -25318,7 +25315,7 @@
         <v>75</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L227" s="2"/>
       <c r="M227" s="2"/>
@@ -25371,7 +25368,7 @@
         <v>75</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>81</v>
@@ -25391,10 +25388,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -25417,7 +25414,7 @@
         <v>75</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L228" s="2"/>
       <c r="M228" s="2"/>
@@ -25470,7 +25467,7 @@
         <v>75</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>81</v>
@@ -25490,10 +25487,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -25516,7 +25513,7 @@
         <v>75</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="L229" s="2"/>
       <c r="M229" s="2"/>
@@ -25569,7 +25566,7 @@
         <v>75</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>81</v>
@@ -25589,13 +25586,13 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B230" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C230" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="B230" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="C230" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="D230" t="s" s="2">
         <v>75</v>
@@ -25617,10 +25614,10 @@
         <v>75</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="M230" s="2"/>
       <c r="N230" s="2"/>
@@ -25672,7 +25669,7 @@
         <v>75</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>81</v>
@@ -25692,10 +25689,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -25793,10 +25790,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -25894,10 +25891,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -25995,10 +25992,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -26096,10 +26093,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -26199,10 +26196,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -26302,10 +26299,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -26405,10 +26402,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -26508,10 +26505,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -26609,10 +26606,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -26649,7 +26646,7 @@
         <v>75</v>
       </c>
       <c r="S240" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="T240" t="s" s="2">
         <v>75</v>
@@ -26668,25 +26665,25 @@
       </c>
       <c r="Y240" s="2"/>
       <c r="Z240" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AA240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE240" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF240" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AA240" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB240" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC240" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD240" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE240" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF240" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>76</v>
@@ -26706,10 +26703,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -26736,7 +26733,7 @@
       </c>
       <c r="L241" s="2"/>
       <c r="M241" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" s="2"/>
@@ -26748,7 +26745,7 @@
         <v>75</v>
       </c>
       <c r="S241" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="T241" t="s" s="2">
         <v>75</v>
@@ -26787,7 +26784,7 @@
         <v>75</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>81</v>
@@ -26807,10 +26804,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -26837,12 +26834,12 @@
       </c>
       <c r="L242" s="2"/>
       <c r="M242" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" s="2"/>
       <c r="P242" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Q242" s="2"/>
       <c r="R242" t="s" s="2">
@@ -26888,7 +26885,7 @@
         <v>75</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>81</v>
@@ -26908,10 +26905,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -26987,7 +26984,7 @@
         <v>75</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>81</v>
@@ -27007,10 +27004,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -27033,7 +27030,7 @@
         <v>75</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L244" s="2"/>
       <c r="M244" s="2"/>
@@ -27086,7 +27083,7 @@
         <v>75</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>81</v>
@@ -27106,10 +27103,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -27132,7 +27129,7 @@
         <v>75</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L245" s="2"/>
       <c r="M245" s="2"/>
@@ -27185,7 +27182,7 @@
         <v>75</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>81</v>
@@ -27205,10 +27202,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -27231,7 +27228,7 @@
         <v>75</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L246" s="2"/>
       <c r="M246" s="2"/>
@@ -27284,7 +27281,7 @@
         <v>75</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>81</v>
@@ -27304,10 +27301,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -27330,7 +27327,7 @@
         <v>75</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="L247" s="2"/>
       <c r="M247" s="2"/>
@@ -27383,7 +27380,7 @@
         <v>75</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>81</v>
@@ -27403,10 +27400,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -27429,7 +27426,7 @@
         <v>75</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="L248" s="2"/>
       <c r="M248" s="2"/>
@@ -27482,7 +27479,7 @@
         <v>75</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>81</v>
@@ -27502,10 +27499,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -27528,7 +27525,7 @@
         <v>75</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L249" s="2"/>
       <c r="M249" s="2"/>
@@ -27581,7 +27578,7 @@
         <v>75</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>81</v>
@@ -27601,10 +27598,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -27627,7 +27624,7 @@
         <v>75</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L250" s="2"/>
       <c r="M250" s="2"/>
@@ -27680,7 +27677,7 @@
         <v>75</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>81</v>
@@ -27700,10 +27697,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -27726,7 +27723,7 @@
         <v>75</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L251" s="2"/>
       <c r="M251" s="2"/>
@@ -27779,7 +27776,7 @@
         <v>75</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>81</v>
@@ -27799,10 +27796,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -27825,7 +27822,7 @@
         <v>75</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L252" s="2"/>
       <c r="M252" s="2"/>
@@ -27878,7 +27875,7 @@
         <v>75</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>81</v>
@@ -27898,10 +27895,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -27924,7 +27921,7 @@
         <v>75</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L253" s="2"/>
       <c r="M253" s="2"/>
@@ -27977,7 +27974,7 @@
         <v>75</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>81</v>
@@ -27997,10 +27994,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -28023,7 +28020,7 @@
         <v>75</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="L254" s="2"/>
       <c r="M254" s="2"/>
@@ -28076,7 +28073,7 @@
         <v>75</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>81</v>
@@ -28096,13 +28093,13 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B255" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C255" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="B255" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="C255" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="D255" t="s" s="2">
         <v>75</v>
@@ -28124,10 +28121,10 @@
         <v>75</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="M255" s="2"/>
       <c r="N255" s="2"/>
@@ -28179,7 +28176,7 @@
         <v>75</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>81</v>
@@ -28199,10 +28196,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -28300,10 +28297,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -28401,10 +28398,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -28502,10 +28499,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -28603,10 +28600,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -28706,10 +28703,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -28809,10 +28806,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -28912,10 +28909,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -29015,10 +29012,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -29116,10 +29113,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -29156,7 +29153,7 @@
         <v>75</v>
       </c>
       <c r="S265" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="T265" t="s" s="2">
         <v>75</v>
@@ -29175,25 +29172,25 @@
       </c>
       <c r="Y265" s="2"/>
       <c r="Z265" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AA265" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB265" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC265" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD265" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE265" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF265" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="AA265" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB265" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC265" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD265" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE265" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF265" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>76</v>
@@ -29213,10 +29210,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -29243,7 +29240,7 @@
       </c>
       <c r="L266" s="2"/>
       <c r="M266" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N266" s="2"/>
       <c r="O266" s="2"/>
@@ -29255,7 +29252,7 @@
         <v>75</v>
       </c>
       <c r="S266" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="T266" t="s" s="2">
         <v>75</v>
@@ -29294,7 +29291,7 @@
         <v>75</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>81</v>
@@ -29314,10 +29311,10 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -29344,12 +29341,12 @@
       </c>
       <c r="L267" s="2"/>
       <c r="M267" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="N267" s="2"/>
       <c r="O267" s="2"/>
       <c r="P267" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Q267" s="2"/>
       <c r="R267" t="s" s="2">
@@ -29395,7 +29392,7 @@
         <v>75</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>81</v>
@@ -29415,10 +29412,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -29494,7 +29491,7 @@
         <v>75</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>81</v>
@@ -29514,10 +29511,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -29540,7 +29537,7 @@
         <v>75</v>
       </c>
       <c r="K269" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L269" s="2"/>
       <c r="M269" s="2"/>
@@ -29593,7 +29590,7 @@
         <v>75</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>81</v>
@@ -29613,10 +29610,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -29639,7 +29636,7 @@
         <v>75</v>
       </c>
       <c r="K270" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L270" s="2"/>
       <c r="M270" s="2"/>
@@ -29692,7 +29689,7 @@
         <v>75</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>81</v>
@@ -29712,10 +29709,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -29738,7 +29735,7 @@
         <v>75</v>
       </c>
       <c r="K271" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L271" s="2"/>
       <c r="M271" s="2"/>
@@ -29791,7 +29788,7 @@
         <v>75</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>81</v>
@@ -29811,10 +29808,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -29837,7 +29834,7 @@
         <v>75</v>
       </c>
       <c r="K272" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="L272" s="2"/>
       <c r="M272" s="2"/>
@@ -29890,7 +29887,7 @@
         <v>75</v>
       </c>
       <c r="AF272" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG272" t="s" s="2">
         <v>81</v>
@@ -29910,10 +29907,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -29936,7 +29933,7 @@
         <v>75</v>
       </c>
       <c r="K273" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="L273" s="2"/>
       <c r="M273" s="2"/>
@@ -29989,7 +29986,7 @@
         <v>75</v>
       </c>
       <c r="AF273" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG273" t="s" s="2">
         <v>81</v>
@@ -30009,10 +30006,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -30035,7 +30032,7 @@
         <v>75</v>
       </c>
       <c r="K274" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L274" s="2"/>
       <c r="M274" s="2"/>
@@ -30088,7 +30085,7 @@
         <v>75</v>
       </c>
       <c r="AF274" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG274" t="s" s="2">
         <v>81</v>
@@ -30108,10 +30105,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -30134,7 +30131,7 @@
         <v>75</v>
       </c>
       <c r="K275" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L275" s="2"/>
       <c r="M275" s="2"/>
@@ -30187,7 +30184,7 @@
         <v>75</v>
       </c>
       <c r="AF275" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG275" t="s" s="2">
         <v>81</v>
@@ -30207,10 +30204,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -30233,7 +30230,7 @@
         <v>75</v>
       </c>
       <c r="K276" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L276" s="2"/>
       <c r="M276" s="2"/>
@@ -30286,7 +30283,7 @@
         <v>75</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>81</v>
@@ -30306,10 +30303,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -30332,7 +30329,7 @@
         <v>75</v>
       </c>
       <c r="K277" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L277" s="2"/>
       <c r="M277" s="2"/>
@@ -30385,7 +30382,7 @@
         <v>75</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>81</v>
@@ -30405,10 +30402,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -30431,7 +30428,7 @@
         <v>75</v>
       </c>
       <c r="K278" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L278" s="2"/>
       <c r="M278" s="2"/>
@@ -30484,7 +30481,7 @@
         <v>75</v>
       </c>
       <c r="AF278" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG278" t="s" s="2">
         <v>81</v>
@@ -30504,10 +30501,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -30530,7 +30527,7 @@
         <v>75</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="L279" s="2"/>
       <c r="M279" s="2"/>
@@ -30583,7 +30580,7 @@
         <v>75</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>81</v>
@@ -30603,10 +30600,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -30629,7 +30626,7 @@
         <v>75</v>
       </c>
       <c r="K280" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="L280" s="2"/>
       <c r="M280" s="2"/>
@@ -30682,7 +30679,7 @@
         <v>75</v>
       </c>
       <c r="AF280" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG280" t="s" s="2">
         <v>81</v>
@@ -30702,10 +30699,10 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -30728,7 +30725,7 @@
         <v>75</v>
       </c>
       <c r="K281" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="L281" s="2"/>
       <c r="M281" s="2"/>
@@ -30781,7 +30778,7 @@
         <v>75</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>81</v>
@@ -30801,10 +30798,10 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -30827,7 +30824,7 @@
         <v>75</v>
       </c>
       <c r="K282" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="L282" s="2"/>
       <c r="M282" s="2"/>
@@ -30880,7 +30877,7 @@
         <v>75</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>81</v>
@@ -30900,10 +30897,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -30926,11 +30923,11 @@
         <v>75</v>
       </c>
       <c r="K283" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="L283" s="2"/>
       <c r="M283" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="N283" s="2"/>
       <c r="O283" s="2"/>
@@ -30981,7 +30978,7 @@
         <v>75</v>
       </c>
       <c r="AF283" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AG283" t="s" s="2">
         <v>81</v>
@@ -31001,10 +30998,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -31102,10 +31099,10 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -31203,10 +31200,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -31304,10 +31301,10 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -31405,10 +31402,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -31508,10 +31505,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -31611,10 +31608,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -31714,10 +31711,10 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" t="s" s="2">
@@ -31817,10 +31814,10 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C292" s="2"/>
       <c r="D292" t="s" s="2">
@@ -31918,10 +31915,10 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -31955,7 +31952,7 @@
       </c>
       <c r="Q293" s="2"/>
       <c r="R293" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="S293" t="s" s="2">
         <v>75</v>
@@ -31977,7 +31974,7 @@
       </c>
       <c r="Y293" s="2"/>
       <c r="Z293" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AA293" t="s" s="2">
         <v>75</v>
@@ -31995,7 +31992,7 @@
         <v>75</v>
       </c>
       <c r="AF293" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AG293" t="s" s="2">
         <v>81</v>
@@ -32015,10 +32012,10 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -32041,7 +32038,7 @@
         <v>75</v>
       </c>
       <c r="K294" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="L294" s="2"/>
       <c r="M294" s="2"/>
@@ -32094,7 +32091,7 @@
         <v>75</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AG294" t="s" s="2">
         <v>76</v>
@@ -32114,10 +32111,10 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -32140,7 +32137,7 @@
         <v>75</v>
       </c>
       <c r="K295" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="L295" s="2"/>
       <c r="M295" s="2"/>
@@ -32193,7 +32190,7 @@
         <v>75</v>
       </c>
       <c r="AF295" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AG295" t="s" s="2">
         <v>81</v>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:04:35+00:00</t>
+    <t>2026-07-29T08:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:58:09+00:00</t>
+    <t>2026-07-29T09:37:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-allergie-ou-hypersensibilite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:37:21+00:00</t>
+    <t>2026-08-03T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
